--- a/artfynd/A 62459-2025 artfynd.xlsx
+++ b/artfynd/A 62459-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132876876</v>
       </c>
       <c r="B2" t="n">
-        <v>84159</v>
+        <v>84161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>132876887</v>
       </c>
       <c r="B3" t="n">
-        <v>84159</v>
+        <v>84161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62459-2025 artfynd.xlsx
+++ b/artfynd/A 62459-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132876876</v>
       </c>
       <c r="B2" t="n">
-        <v>84161</v>
+        <v>84162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>132876887</v>
       </c>
       <c r="B3" t="n">
-        <v>84161</v>
+        <v>84162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62459-2025 artfynd.xlsx
+++ b/artfynd/A 62459-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132876876</v>
       </c>
       <c r="B2" t="n">
-        <v>84166</v>
+        <v>84167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>132876887</v>
       </c>
       <c r="B3" t="n">
-        <v>84166</v>
+        <v>84167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
